--- a/nano_toolkit_framework/documents/ESP32_開発環境.xlsx
+++ b/nano_toolkit_framework/documents/ESP32_開発環境.xlsx
@@ -8,18 +8,18 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="License" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="はじめに" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="開発環境の概要" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="環境構築手順 （ESP-IDF）" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="環境構築手順 （Eclipse）" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="環境構築手順（EclipsePlugin）" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="環境構築手順（wolfSSL）" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="開発環境更新メモ" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="トラブル対応" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="メモリ設定" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="パーティションテーブル" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="凡例" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="License" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="はじめに" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="開発環境の概要" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="環境構築手順 （ESP-IDF）" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="環境構築手順 （Eclipse）" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="環境構築手順（EclipsePlugin）" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="環境構築手順（wolfSSL）" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="開発環境更新メモ" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="トラブル対応" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="メモリ設定" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="パーティションテーブル" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="凡例" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="392">
-  <si>
-    <t xml:space="preserve">Copyright 2024 Kakuheiki.Nakanohito</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="394">
+  <si>
+    <t xml:space="preserve">Copyright 2024 Nakanohito</t>
   </si>
   <si>
     <t xml:space="preserve">Permission is hereby granted, free of charge, to any</t>
@@ -387,7 +387,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -397,7 +397,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -407,7 +407,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -417,7 +417,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -429,7 +429,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -439,7 +439,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -449,7 +449,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -459,7 +459,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -471,7 +471,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -481,7 +481,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -502,7 +502,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -512,7 +512,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -522,7 +522,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -543,7 +543,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -553,7 +553,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -563,7 +563,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -573,7 +573,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -583,7 +583,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -829,7 +829,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -839,7 +839,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -849,7 +849,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -859,7 +859,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
         <charset val="1"/>
@@ -869,7 +869,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -980,7 +980,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1000,7 +1000,7 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <rFont val="Yu Gothic"/>
         <family val="2"/>
         <charset val="1"/>
@@ -1016,6 +1016,12 @@
   </si>
   <si>
     <t xml:space="preserve">C:\Users\seeke\.espressif\tools\xtensa-esp32-elf\esp-12.2.0_20230208\xtensa-esp32-elf\bin\xtensa-esp32-elf-addr2line.exe -pfiaC -e "D:\ESP32\esptools\workspace\alarm\build\app-template.elf" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">・ESP32-C6の場合は次の場所</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C:\Users\ユーザー名\.espressif\tools\riscv32-esp-elf\esp-14.2.0_20241119\riscv32-esp-elf\bin\riscv32-esp-elf-addr2line.exe -pfiaC -e "elfファイルパス" Backtraceの記述</t>
   </si>
   <si>
     <t xml:space="preserve">１．FreeRTOSの設定</t>
@@ -1472,7 +1478,7 @@
   <fonts count="21">
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1497,21 +1503,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1534,21 +1540,21 @@
     <font>
       <u val="single"/>
       <sz val="11"/>
-      <color rgb="FF0563C1"/>
+      <color theme="10"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1556,35 +1562,35 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="游明朝"/>
+      <color theme="0"/>
+      <name val="Noto Serif JP"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="128"/>
@@ -1598,21 +1604,21 @@
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1627,7 +1633,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
@@ -1639,7 +1645,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAE3F3"/>
+        <fgColor theme="8" tint="0.7999"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
@@ -2002,13 +2008,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>210240</xdr:colOff>
-      <xdr:row>128</xdr:row>
-      <xdr:rowOff>205200</xdr:rowOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>33840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2027,6 +2033,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -2066,6 +2073,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -2106,6 +2114,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2130,13 +2139,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>210240</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>100440</xdr:rowOff>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2155,6 +2164,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -2169,13 +2179,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>77760</xdr:rowOff>
+      <xdr:rowOff>115920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>172080</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>198000</xdr:rowOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2195,6 +2205,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2219,13 +2230,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
       <xdr:row>132</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>134</xdr:row>
-      <xdr:rowOff>34200</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2241,7 +2252,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -2267,16 +2278,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>export IDF_PATH="D:/ESP32/msys32/home/ThinkUser/esp-idf"</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2285,8 +2298,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2298,13 +2312,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>34560</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>69120</xdr:rowOff>
+      <xdr:rowOff>107280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>172080</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2324,6 +2338,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2348,13 +2363,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>146</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>201960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2370,7 +2385,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -2396,16 +2411,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>mkdir -p ~/workspace</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2415,16 +2432,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>cd ./workspace</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2433,8 +2452,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2446,13 +2466,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>151</xdr:row>
-      <xdr:rowOff>34200</xdr:rowOff>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2468,7 +2488,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -2494,20 +2514,22 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>cp -r $IDF_PATH/examples/get-started/hello_world .</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr>
+          <a:pPr defTabSz="914400">
             <a:lnSpc>
               <a:spcPct val="100000"/>
             </a:lnSpc>
@@ -2516,29 +2538,32 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>cd </a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>~/workspace/hello_world</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr>
+          <a:pPr defTabSz="914400">
             <a:lnSpc>
               <a:spcPct val="100000"/>
             </a:lnSpc>
@@ -2546,8 +2571,9 @@
               <a:tab algn="l" pos="0"/>
             </a:tabLst>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2559,13 +2585,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
       <xdr:row>137</xdr:row>
-      <xdr:rowOff>129240</xdr:rowOff>
+      <xdr:rowOff>167400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>139</xdr:row>
-      <xdr:rowOff>77040</xdr:rowOff>
+      <xdr:rowOff>114840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2581,7 +2607,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -2607,16 +2633,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>printenv IDF_PATH</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2625,8 +2653,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2638,13 +2667,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
       <xdr:row>175</xdr:row>
-      <xdr:rowOff>77760</xdr:rowOff>
+      <xdr:rowOff>115560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>177</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2660,7 +2689,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -2686,16 +2715,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>make menuconfig</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -2704,8 +2735,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2717,13 +2749,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>179</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>196</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2742,6 +2774,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -2756,13 +2789,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>95040</xdr:colOff>
       <xdr:row>187</xdr:row>
-      <xdr:rowOff>95040</xdr:rowOff>
+      <xdr:rowOff>132840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>103320</xdr:colOff>
       <xdr:row>188</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>201960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2782,6 +2815,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2806,13 +2840,13 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>181080</xdr:colOff>
       <xdr:row>187</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>85680</xdr:colOff>
       <xdr:row>189</xdr:row>
-      <xdr:rowOff>51480</xdr:rowOff>
+      <xdr:rowOff>89640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2833,10 +2867,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2864,43 +2899,48 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>カーソルで</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>"Serial flasher config"</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>を選択して</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>Enter</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -2912,13 +2952,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>198</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>116640</xdr:colOff>
       <xdr:row>229</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>95040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2937,6 +2977,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2949,13 +2990,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>69120</xdr:colOff>
       <xdr:row>218</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>198000</xdr:colOff>
       <xdr:row>220</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>201960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2975,6 +3016,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -2999,13 +3041,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>231</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>248</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3024,6 +3066,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3036,13 +3079,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
       <xdr:row>237</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>189360</xdr:colOff>
       <xdr:row>239</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3062,6 +3105,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3086,13 +3130,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>251</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>268</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3111,6 +3155,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3123,13 +3168,13 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>95040</xdr:colOff>
       <xdr:row>265</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
       <xdr:row>266</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:rowOff>184680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3149,6 +3194,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3173,13 +3219,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>294</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>154800</xdr:colOff>
       <xdr:row>295</xdr:row>
-      <xdr:rowOff>163440</xdr:rowOff>
+      <xdr:rowOff>201240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3195,7 +3241,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -3221,16 +3267,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>make flash</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -3239,8 +3287,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1200" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -3252,13 +3301,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>153</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>170</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3277,6 +3326,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3289,13 +3339,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>271</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>288</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3314,6 +3364,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3326,13 +3377,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>298</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>315</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3351,6 +3402,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3363,13 +3415,13 @@
       <xdr:col>30</xdr:col>
       <xdr:colOff>86400</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3390,10 +3442,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3421,16 +3474,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>テキストファイルとして作成</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -3442,13 +3497,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3467,6 +3522,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3483,14 +3539,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>162360</xdr:colOff>
-      <xdr:row>213</xdr:row>
-      <xdr:rowOff>203040</xdr:rowOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>61920</xdr:colOff>
-      <xdr:row>239</xdr:row>
-      <xdr:rowOff>149760</xdr:rowOff>
+      <xdr:row>240</xdr:row>
+      <xdr:rowOff>64080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3509,6 +3565,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3521,13 +3578,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>210240</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>102240</xdr:rowOff>
+      <xdr:rowOff>111600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3546,6 +3603,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -3560,13 +3618,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>25920</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>129240</xdr:rowOff>
+      <xdr:rowOff>138960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198000</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>128880</xdr:rowOff>
+      <xdr:rowOff>138600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3586,6 +3644,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3610,13 +3669,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>57960</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>174960</xdr:rowOff>
+      <xdr:rowOff>184680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3635,6 +3694,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -3649,13 +3709,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>17280</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>25920</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>146160</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:rowOff>104040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3675,6 +3735,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3699,13 +3760,13 @@
       <xdr:col>21</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>164520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>146160</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
+      <xdr:rowOff>147240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3725,6 +3786,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3749,13 +3811,13 @@
       <xdr:col>29</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>164520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>128880</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
+      <xdr:rowOff>147240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3775,6 +3837,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3799,13 +3862,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>129600</xdr:colOff>
       <xdr:row>108</xdr:row>
-      <xdr:rowOff>130320</xdr:rowOff>
+      <xdr:rowOff>139680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3824,6 +3887,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -3838,13 +3902,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>97200</xdr:colOff>
       <xdr:row>141</xdr:row>
-      <xdr:rowOff>1440</xdr:rowOff>
+      <xdr:rowOff>10800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3863,6 +3927,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -3875,13 +3940,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>43200</xdr:colOff>
       <xdr:row>128</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:rowOff>207720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>206640</xdr:rowOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>6480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3901,6 +3966,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3924,14 +3990,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>207000</xdr:rowOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>6840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>180720</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>77400</xdr:rowOff>
+      <xdr:rowOff>86760</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3951,6 +4017,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3975,13 +4042,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
       <xdr:colOff>97200</xdr:colOff>
       <xdr:row>169</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4000,6 +4067,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -4012,13 +4080,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>162</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>189360</xdr:colOff>
       <xdr:row>164</xdr:row>
-      <xdr:rowOff>34200</xdr:rowOff>
+      <xdr:rowOff>43560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4038,6 +4106,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4062,13 +4131,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>163800</xdr:colOff>
       <xdr:row>158</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>18360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>163440</xdr:colOff>
       <xdr:row>159</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:rowOff>104400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4088,6 +4157,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4112,13 +4182,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>8640</xdr:colOff>
       <xdr:row>164</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>42840</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4139,10 +4209,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4170,16 +4241,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>チェックを外す</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4191,13 +4264,13 @@
       <xdr:col>10</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
       <xdr:row>159</xdr:row>
-      <xdr:rowOff>51840</xdr:rowOff>
+      <xdr:rowOff>61560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>137520</xdr:colOff>
       <xdr:row>160</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:rowOff>156240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4218,10 +4291,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4249,16 +4323,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>選択する</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4270,13 +4346,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>180</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>66600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>112680</xdr:colOff>
-      <xdr:row>205</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4295,6 +4371,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -4307,13 +4384,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>86400</xdr:colOff>
       <xdr:row>190</xdr:row>
-      <xdr:rowOff>129240</xdr:rowOff>
+      <xdr:rowOff>195840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
-      <xdr:row>191</xdr:row>
-      <xdr:rowOff>209160</xdr:rowOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>66240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4333,6 +4410,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4357,13 +4435,13 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>188</xdr:row>
-      <xdr:rowOff>51840</xdr:rowOff>
+      <xdr:rowOff>118440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>172080</xdr:colOff>
-      <xdr:row>189</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>3600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4384,10 +4462,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4415,16 +4494,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>チェックを外す</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4435,14 +4516,14 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>207000</xdr:colOff>
-      <xdr:row>191</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>55440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>180720</xdr:colOff>
       <xdr:row>193</xdr:row>
-      <xdr:rowOff>68760</xdr:rowOff>
+      <xdr:rowOff>135360</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4462,6 +4543,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4486,13 +4568,13 @@
       <xdr:col>27</xdr:col>
       <xdr:colOff>188280</xdr:colOff>
       <xdr:row>187</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>50</xdr:col>
       <xdr:colOff>162000</xdr:colOff>
-      <xdr:row>190</xdr:row>
-      <xdr:rowOff>207360</xdr:rowOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>64440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4513,10 +4595,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4544,16 +4627,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>コマンドを書き換える</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -4563,70 +4648,78 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>※</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>ESP-IDF4.2</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>の時点では、</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>home</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>ディレクトリ配下に</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>esp-idf</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>フォルダが</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -4636,16 +4729,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>　無い場合のみ指定することになっている。</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -4654,8 +4749,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4666,14 +4762,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>34560</xdr:colOff>
-      <xdr:row>223</xdr:row>
-      <xdr:rowOff>112320</xdr:rowOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>26640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
-      <xdr:row>224</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>112680</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4693,6 +4789,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4717,13 +4814,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>34560</xdr:colOff>
       <xdr:row>226</xdr:row>
-      <xdr:rowOff>51840</xdr:rowOff>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
-      <xdr:row>227</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:row>228</xdr:row>
+      <xdr:rowOff>52200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4743,6 +4840,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4766,14 +4864,14 @@
     <xdr:from>
       <xdr:col>22</xdr:col>
       <xdr:colOff>60480</xdr:colOff>
-      <xdr:row>221</xdr:row>
-      <xdr:rowOff>112320</xdr:rowOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>26280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>68760</xdr:colOff>
-      <xdr:row>222</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>69120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4794,10 +4892,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4825,16 +4924,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>追加する</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4846,13 +4947,13 @@
       <xdr:col>27</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>224</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>132480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>146160</xdr:colOff>
       <xdr:row>225</xdr:row>
-      <xdr:rowOff>51480</xdr:rowOff>
+      <xdr:rowOff>175320</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4873,10 +4974,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4904,16 +5006,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>追加する</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -4925,13 +5029,13 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>34560</xdr:colOff>
       <xdr:row>228</xdr:row>
-      <xdr:rowOff>25920</xdr:rowOff>
+      <xdr:rowOff>149760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
-      <xdr:row>229</xdr:row>
-      <xdr:rowOff>111960</xdr:rowOff>
+      <xdr:row>230</xdr:row>
+      <xdr:rowOff>26280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4951,6 +5055,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -4974,14 +5079,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>25920</xdr:colOff>
-      <xdr:row>230</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>77400</xdr:colOff>
-      <xdr:row>232</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:row>233</xdr:row>
+      <xdr:rowOff>104040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5002,10 +5107,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5033,16 +5139,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>D:\ESP32\msys32\usr\bin;D:\ESP32\msys32\mingw32\bin;D:\ESP32\msys32\opt\xtensa-esp32-elf\bin</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -5052,16 +5160,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>に書き換える</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -5070,8 +5180,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5083,13 +5194,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>291</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>7200</xdr:colOff>
-      <xdr:row>319</xdr:row>
-      <xdr:rowOff>42840</xdr:rowOff>
+      <xdr:row>320</xdr:row>
+      <xdr:rowOff>4680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5108,6 +5219,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -5119,14 +5231,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>181080</xdr:colOff>
-      <xdr:row>309</xdr:row>
-      <xdr:rowOff>51840</xdr:rowOff>
+      <xdr:row>310</xdr:row>
+      <xdr:rowOff>13680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>60120</xdr:colOff>
-      <xdr:row>310</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:row>311</xdr:row>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5146,6 +5258,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5169,14 +5282,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>181080</xdr:colOff>
-      <xdr:row>300</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:row>301</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
-      <xdr:row>301</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:row>302</xdr:row>
+      <xdr:rowOff>134280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5196,6 +5309,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5219,14 +5333,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>60480</xdr:colOff>
-      <xdr:row>298</xdr:row>
-      <xdr:rowOff>77760</xdr:rowOff>
+      <xdr:row>299</xdr:row>
+      <xdr:rowOff>39600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>68760</xdr:colOff>
-      <xdr:row>299</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:row>300</xdr:row>
+      <xdr:rowOff>82440</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5247,10 +5361,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5278,16 +5393,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>選択する</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5298,14 +5415,14 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>86400</xdr:colOff>
-      <xdr:row>310</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:row>311</xdr:row>
+      <xdr:rowOff>99720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>312</xdr:row>
-      <xdr:rowOff>25200</xdr:rowOff>
+      <xdr:rowOff>196560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5326,10 +5443,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5357,16 +5475,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>書き換える</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5378,13 +5498,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>250</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>162000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>49</xdr:col>
       <xdr:colOff>54000</xdr:colOff>
       <xdr:row>284</xdr:row>
-      <xdr:rowOff>29160</xdr:rowOff>
+      <xdr:rowOff>190800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5403,6 +5523,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -5415,13 +5536,13 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>207000</xdr:colOff>
       <xdr:row>271</xdr:row>
-      <xdr:rowOff>34560</xdr:rowOff>
+      <xdr:rowOff>196200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>34200</xdr:colOff>
-      <xdr:row>272</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5441,6 +5562,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5464,14 +5586,14 @@
     <xdr:from>
       <xdr:col>32</xdr:col>
       <xdr:colOff>77760</xdr:colOff>
-      <xdr:row>272</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>98640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
       <xdr:row>274</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>187560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5492,10 +5614,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5523,16 +5646,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>書き換える</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5544,13 +5669,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>326</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>171360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>187200</xdr:colOff>
       <xdr:row>345</xdr:row>
-      <xdr:rowOff>16200</xdr:rowOff>
+      <xdr:rowOff>187560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5569,6 +5694,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -5581,13 +5707,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>120600</xdr:colOff>
       <xdr:row>328</xdr:row>
-      <xdr:rowOff>25920</xdr:rowOff>
+      <xdr:rowOff>197640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>68400</xdr:colOff>
-      <xdr:row>329</xdr:row>
-      <xdr:rowOff>111960</xdr:rowOff>
+      <xdr:row>330</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5607,6 +5733,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5630,14 +5757,14 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>51840</xdr:colOff>
-      <xdr:row>329</xdr:row>
-      <xdr:rowOff>77760</xdr:rowOff>
+      <xdr:row>330</xdr:row>
+      <xdr:rowOff>39600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>103320</xdr:colOff>
-      <xdr:row>330</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:row>331</xdr:row>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5658,10 +5785,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5689,25 +5817,28 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>"flash"</a:t>
           </a:r>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>と書く</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5719,13 +5850,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>347</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>171360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>720</xdr:colOff>
-      <xdr:row>365</xdr:row>
-      <xdr:rowOff>165240</xdr:rowOff>
+      <xdr:row>366</xdr:row>
+      <xdr:rowOff>127080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5744,6 +5875,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -5756,13 +5888,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>351</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>189000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>214920</xdr:colOff>
-      <xdr:row>352</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:row>353</xdr:row>
+      <xdr:rowOff>65520</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5782,6 +5914,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5805,14 +5938,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>34560</xdr:colOff>
-      <xdr:row>352</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:row>353</xdr:row>
+      <xdr:rowOff>126000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>86040</xdr:colOff>
-      <xdr:row>354</xdr:row>
-      <xdr:rowOff>51120</xdr:rowOff>
+      <xdr:row>355</xdr:row>
+      <xdr:rowOff>12960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5833,10 +5966,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5864,16 +5998,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>選択する</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -5884,14 +6020,14 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>112320</xdr:colOff>
-      <xdr:row>363</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:row>364</xdr:row>
+      <xdr:rowOff>117360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>111960</xdr:colOff>
       <xdr:row>365</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>197280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5911,6 +6047,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5935,13 +6072,13 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>360</xdr:colOff>
       <xdr:row>167</xdr:row>
-      <xdr:rowOff>112320</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>180720</xdr:colOff>
       <xdr:row>168</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:rowOff>207720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -5961,6 +6098,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5985,13 +6123,13 @@
       <xdr:col>36</xdr:col>
       <xdr:colOff>86400</xdr:colOff>
       <xdr:row>201</xdr:row>
-      <xdr:rowOff>129240</xdr:rowOff>
+      <xdr:rowOff>195840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>77400</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>209160</xdr:rowOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>66240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6011,6 +6149,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6035,13 +6174,13 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>86400</xdr:colOff>
       <xdr:row>343</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>60120</xdr:colOff>
-      <xdr:row>344</xdr:row>
-      <xdr:rowOff>103320</xdr:rowOff>
+      <xdr:row>345</xdr:row>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6061,6 +6200,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6085,13 +6225,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>78840</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>2160</xdr:rowOff>
+      <xdr:rowOff>11880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6110,6 +6250,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6122,13 +6263,13 @@
       <xdr:col>33</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>62</xdr:col>
       <xdr:colOff>78840</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>2160</xdr:rowOff>
+      <xdr:rowOff>11880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6147,6 +6288,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6164,13 +6306,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>28440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>120240</xdr:colOff>
       <xdr:row>115</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:rowOff>209160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6189,6 +6331,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -6203,13 +6346,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>103680</xdr:colOff>
       <xdr:row>108</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>114840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>8280</xdr:colOff>
       <xdr:row>109</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>183600</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6229,6 +6372,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6253,13 +6397,13 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>129240</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>200880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>25200</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6279,6 +6423,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6303,13 +6448,13 @@
       <xdr:col>23</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
       <xdr:row>92</xdr:row>
-      <xdr:rowOff>172440</xdr:rowOff>
+      <xdr:rowOff>200880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>51120</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>183240</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6329,6 +6474,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6378,6 +6524,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -6392,13 +6539,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>163</xdr:row>
-      <xdr:rowOff>34560</xdr:rowOff>
+      <xdr:rowOff>72360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>163800</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>185040</xdr:rowOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>13680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6417,6 +6564,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6429,13 +6577,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>175</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>214920</xdr:colOff>
-      <xdr:row>202</xdr:row>
-      <xdr:rowOff>192240</xdr:rowOff>
+      <xdr:row>203</xdr:row>
+      <xdr:rowOff>20880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6454,6 +6602,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6465,14 +6614,14 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>112320</xdr:colOff>
-      <xdr:row>200</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>25560</xdr:colOff>
       <xdr:row>202</xdr:row>
-      <xdr:rowOff>60120</xdr:rowOff>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6492,6 +6641,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6515,14 +6665,14 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>172440</xdr:colOff>
-      <xdr:row>259</xdr:row>
-      <xdr:rowOff>207000</xdr:rowOff>
+      <xdr:row>260</xdr:row>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>8280</xdr:colOff>
       <xdr:row>261</xdr:row>
-      <xdr:rowOff>68760</xdr:rowOff>
+      <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6542,6 +6692,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6566,13 +6717,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
       <xdr:colOff>77400</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>111960</xdr:rowOff>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6591,6 +6742,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -6605,13 +6757,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>198000</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
+      <xdr:rowOff>156600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6630,6 +6782,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -6644,13 +6797,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>28440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>192600</xdr:colOff>
       <xdr:row>137</xdr:row>
-      <xdr:rowOff>127440</xdr:rowOff>
+      <xdr:rowOff>156240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6669,6 +6822,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6681,13 +6835,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>143</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>28440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>97200</xdr:colOff>
       <xdr:row>156</xdr:row>
-      <xdr:rowOff>167400</xdr:rowOff>
+      <xdr:rowOff>195840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6706,6 +6860,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -6720,13 +6875,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>206</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>199080</xdr:colOff>
-      <xdr:row>233</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:row>234</xdr:row>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6745,6 +6900,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6756,14 +6912,14 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>103680</xdr:colOff>
-      <xdr:row>169</xdr:row>
-      <xdr:rowOff>181080</xdr:rowOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>171</xdr:row>
-      <xdr:rowOff>42840</xdr:rowOff>
+      <xdr:rowOff>81000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6783,6 +6939,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6806,14 +6963,14 @@
     <xdr:from>
       <xdr:col>28</xdr:col>
       <xdr:colOff>103680</xdr:colOff>
-      <xdr:row>231</xdr:row>
-      <xdr:rowOff>198360</xdr:rowOff>
+      <xdr:row>232</xdr:row>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>16920</xdr:colOff>
       <xdr:row>233</xdr:row>
-      <xdr:rowOff>60120</xdr:rowOff>
+      <xdr:rowOff>98280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6833,6 +6990,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6857,13 +7015,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>237</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>206640</xdr:colOff>
-      <xdr:row>264</xdr:row>
-      <xdr:rowOff>186120</xdr:rowOff>
+      <xdr:row>265</xdr:row>
+      <xdr:rowOff>14760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6882,6 +7040,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -6893,14 +7052,14 @@
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>43200</xdr:colOff>
-      <xdr:row>262</xdr:row>
-      <xdr:rowOff>207000</xdr:rowOff>
+      <xdr:row>263</xdr:row>
+      <xdr:rowOff>35640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>172080</xdr:colOff>
       <xdr:row>264</xdr:row>
-      <xdr:rowOff>68760</xdr:rowOff>
+      <xdr:rowOff>106920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6920,6 +7079,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6943,14 +7103,14 @@
     <xdr:from>
       <xdr:col>24</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
-      <xdr:row>257</xdr:row>
-      <xdr:rowOff>207000</xdr:rowOff>
+      <xdr:row>258</xdr:row>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>259</xdr:row>
-      <xdr:rowOff>68760</xdr:rowOff>
+      <xdr:rowOff>106560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -6970,6 +7130,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6994,13 +7155,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>268</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>206640</xdr:colOff>
       <xdr:row>300</xdr:row>
-      <xdr:rowOff>1800</xdr:rowOff>
+      <xdr:rowOff>39960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7019,6 +7180,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -7031,13 +7193,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>155160</xdr:colOff>
       <xdr:row>272</xdr:row>
-      <xdr:rowOff>163800</xdr:rowOff>
+      <xdr:rowOff>201960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>102960</xdr:colOff>
       <xdr:row>274</xdr:row>
-      <xdr:rowOff>25560</xdr:rowOff>
+      <xdr:rowOff>63720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7057,6 +7219,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -7081,13 +7244,13 @@
       <xdr:col>32</xdr:col>
       <xdr:colOff>43200</xdr:colOff>
       <xdr:row>298</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>46800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>42840</xdr:colOff>
       <xdr:row>299</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7107,6 +7270,7 @@
           <a:solidFill>
             <a:srgbClr val="ff0000"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -7131,13 +7295,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>303</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
       <xdr:colOff>52200</xdr:colOff>
       <xdr:row>326</xdr:row>
-      <xdr:rowOff>153720</xdr:rowOff>
+      <xdr:rowOff>191880</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7169,6 +7333,7 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
+          <a:noFill/>
           <a:ln w="0">
             <a:noFill/>
           </a:ln>
@@ -7192,6 +7357,7 @@
             <a:solidFill>
               <a:srgbClr val="ff0000"/>
             </a:solidFill>
+            <a:miter/>
           </a:ln>
         </xdr:spPr>
         <xdr:style>
@@ -7227,6 +7393,7 @@
             <a:solidFill>
               <a:srgbClr val="ff0000"/>
             </a:solidFill>
+            <a:miter/>
           </a:ln>
         </xdr:spPr>
         <xdr:style>
@@ -7252,13 +7419,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>330</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>204840</xdr:colOff>
       <xdr:row>336</xdr:row>
-      <xdr:rowOff>67680</xdr:rowOff>
+      <xdr:rowOff>105840</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7290,6 +7457,7 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
+          <a:noFill/>
           <a:ln w="0">
             <a:noFill/>
           </a:ln>
@@ -7313,6 +7481,7 @@
             <a:solidFill>
               <a:srgbClr val="ff0000"/>
             </a:solidFill>
+            <a:miter/>
           </a:ln>
         </xdr:spPr>
         <xdr:style>
@@ -7338,13 +7507,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>342</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>163800</xdr:colOff>
       <xdr:row>355</xdr:row>
-      <xdr:rowOff>167400</xdr:rowOff>
+      <xdr:rowOff>205200</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7376,6 +7545,7 @@
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
+          <a:noFill/>
           <a:ln w="0">
             <a:noFill/>
           </a:ln>
@@ -7399,6 +7569,7 @@
             <a:solidFill>
               <a:srgbClr val="ff0000"/>
             </a:solidFill>
+            <a:miter/>
           </a:ln>
         </xdr:spPr>
         <xdr:style>
@@ -7424,13 +7595,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>359</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>129600</xdr:colOff>
       <xdr:row>381</xdr:row>
-      <xdr:rowOff>121680</xdr:rowOff>
+      <xdr:rowOff>159840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7449,6 +7620,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -7466,13 +7638,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>114120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7491,6 +7663,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -7503,13 +7676,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>46800</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>110160</xdr:rowOff>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7528,6 +7701,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -7542,13 +7716,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>46800</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>110160</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7567,6 +7741,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -7581,13 +7756,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
       <xdr:colOff>46800</xdr:colOff>
       <xdr:row>134</xdr:row>
-      <xdr:rowOff>110160</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7606,6 +7781,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -7620,13 +7796,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>57</xdr:col>
       <xdr:colOff>30240</xdr:colOff>
       <xdr:row>163</xdr:row>
-      <xdr:rowOff>81720</xdr:rowOff>
+      <xdr:rowOff>91080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7645,6 +7821,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
             <a:srgbClr val="000000"/>
@@ -7659,13 +7836,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>207000</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>146520</xdr:rowOff>
+      <xdr:rowOff>156240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>86040</xdr:colOff>
       <xdr:row>152</xdr:row>
-      <xdr:rowOff>51120</xdr:rowOff>
+      <xdr:rowOff>60480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7702,13 +7879,13 @@
       <xdr:col>25</xdr:col>
       <xdr:colOff>137880</xdr:colOff>
       <xdr:row>149</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>9720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>102960</xdr:colOff>
       <xdr:row>150</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>95400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -7729,10 +7906,11 @@
         <a:solidFill>
           <a:srgbClr val="5b9bd5"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
             <a:srgbClr val="43729d"/>
           </a:solidFill>
+          <a:miter/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -7760,16 +7938,18 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="ja-JP" sz="1100" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="ja-JP" sz="1100" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
             <a:t>この二つをコメント解除する。</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1100" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1100" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7808,7 +7988,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -7834,17 +8014,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>IOError: D:/ESP32/msys32/home/ThinkUser/esp-idf/Kconfig:59: Could not open '/home/ThinkUser/esp-idf/components/bootloader/Kconfig.projbuild' (ENOENT: No such file or directory). Perhaps the $srctree environment variable (which was unset) is set incorrectly. Note that the current value of $srctree is saved when the Kconfig instance is created (for consistency and to cleanly separate instances). Also note that e.g. $FOO in a 'source' statement does not refer to the environment variable FOO, but rather to the Kconfig Symbol FOO (which would commonly have 'option env="FOO"' in its definition).</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7854,17 +8036,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>make: *** [/home/ThinkUser/esp-idf/components/esp32/Makefile.projbuild:51: /home/ThinkUser/workspace/hello_world/build/esp32/esp32.common.ld] Error 1</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7874,17 +8058,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>xtensa-esp32-elf-ar cru libwpa_supplicant.a src/crypto/ms_funcs.o src/crypto/crypto_internal-cipher.o src/crypto/crypto_internal-modexp.o src/crypto/bignum.o src/crypto/sha1-pbkdf2.o src/crypto/aes-cbc.o src/crypto/md5.o src/crypto/rc4.o src/crypto/sha256.o src/crypto/dh_groups.o src/crypto/md4-internal.o src/crypto/sha1-internal.o src/crypto/aes-wrap.o src/crypto/crypto_mbedtls.o src/crypto/crypto_internal.o src/crypto/dh_group5.o src/crypto/des-internal.o src/crypto/crypto_internal-rsa.o src/crypto/aes-unwrap.o src/crypto/aes-internal-dec.o src/crypto/sha1.o src/crypto/aes-internal.o src/crypto/md5-internal.o src/crypto/sha256-internal.o src/crypto/aes-internal-enc.o port/os_xtensa.o src/fast_crypto/fast_crypto_internal-cipher.o src/fast_crypto/fast_crypto_internal-modexp.o src/fast_crypto/fast_aes-unwrap.o src/fast_crypto/fast_sha256.o src/fast_crypto/fast_crypto_internal.o src/fast_crypto/fast_aes-cbc.o src/fast_crypto/fast_sha256-internal.o src/fast_crypto/fast_aes-wrap.o src/wpa2/eap_peer/eap_peap_common.o src/wpa2/eap_peer/chap.o src/wpa2/eap_peer/eap_mschapv2.o src/wpa2/eap_peer/eap_peap.o src/wpa2/eap_peer/eap_ttls.o src/wpa2/eap_peer/eap_tls_common.o src/wpa2/eap_peer/eap_tls.o src/wpa2/eap_peer/mschapv2.o src/wpa2/eap_peer/eap_common.o src/wpa2/eap_peer/eap.o src/wpa2/tls/tls_internal.o src/wpa2/tls/tlsv1_common.o src/wpa2/tls/tlsv1_server_write.o src/wpa2/tls/bignum.o src/wpa2/tls/tlsv1_record.o src/wpa2/tls/pkcs5.o src/wpa2/tls/pkcs1.o src/wpa2/tls/tlsv1_client_write.o src/wpa2/tls/tlsv1_server_read.o src/wpa2/tls/asn1.o src/wpa2/tls/pkcs8.o src/wpa2/tls/rsa.o src/wpa2/tls/tlsv1_client.o src/wpa2/tls/tlsv1_client_read.o src/wpa2/tls/tlsv1_cred.o src/wpa2/tls/x509v3.o src/wpa2/tls/tlsv1_server.o src/wpa2/utils/ext_password.o src/wpa2/utils/base64.o src/wps/wps_enrollee.o src/wps/uuid.o src/wps/wps_attr_build.o src/wps/wps_registrar.o src/wps/wps_common.o src/wps/wps.o src/wps/wps_dev_attr.o src/wps/wps_attr_parse.o src/wps/wps_validate.o src/wps/wps_attr_process.o src/wps/eap_common.o</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7893,8 +8079,9 @@
               <a:spcPct val="100000"/>
             </a:lnSpc>
           </a:pPr>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -7928,7 +8115,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -7954,17 +8141,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>ifdef MSYSTEM</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7974,17 +8163,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t># kconfiglib requires Windows-style paths for kconfig files</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -7994,17 +8185,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>COMPONENT_KCONFIGS := $(shell cygpath -w $(COMPONENT_KCONFIGS))</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8014,17 +8207,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>COMPONENT_KCONFIGS_PROJBUILD := $(shell cygpath -w $(COMPONENT_KCONFIGS_PROJBUILD))</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8034,17 +8229,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>endif</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8078,7 +8275,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="ffffff"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -8104,17 +8301,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>#ifdef MSYSTEM</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8124,17 +8323,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t># kconfiglib requires Windows-style paths for kconfig files</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8144,17 +8345,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>COMPONENT_KCONFIGS := $(shell cygpath -w $(COMPONENT_KCONFIGS))</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8164,17 +8367,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>COMPONENT_KCONFIGS_PROJBUILD := $(shell cygpath -w $(COMPONENT_KCONFIGS_PROJBUILD))</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8184,17 +8389,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>#endif</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="900" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="900" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8206,13 +8413,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8231,6 +8438,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -8243,13 +8451,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>40680</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8268,6 +8476,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -8280,13 +8489,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>59760</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>142920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -8305,6 +8514,7 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -8344,10 +8554,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent6">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
+          <a:srgbClr val="e2f0d9"/>
         </a:solidFill>
         <a:ln w="9525">
           <a:solidFill>
@@ -8373,17 +8580,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t># Name,   Type, SubType,  Offset,   Size,  Flags</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8393,17 +8602,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>nvs,      data, nvs,      0x9000,  0x4000</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8413,17 +8624,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>otadata,  data, ota,      0xd000,  0x2000</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8433,17 +8646,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>phy_init, data, phy,      0xf000,  0x1000</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8453,17 +8668,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>factory,  app,  factory,  0x10000,  1M</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8473,17 +8690,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>ota_0,    app,  ota_0,    ,         1M</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8493,17 +8712,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>ota_1,    app,  ota_1,    ,         1M</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
@@ -8513,17 +8734,19 @@
             </a:lnSpc>
           </a:pPr>
           <a:r>
-            <a:rPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
+            <a:rPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="ＭＳ ゴシック"/>
               <a:ea typeface="ＭＳ ゴシック"/>
             </a:rPr>
             <a:t>nvs_key,  data, nvs_keys, ,        0x1000</a:t>
           </a:r>
-          <a:endParaRPr b="0" lang="en-US" sz="1000" spc="-1" strike="noStrike">
-            <a:latin typeface="游明朝"/>
+          <a:endParaRPr b="0" lang="en-US" sz="1000" strike="noStrike" u="none">
+            <a:uFillTx/>
+            <a:latin typeface="Noto Serif JP"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8531,6 +8754,178 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546a"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="e7e6e6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5b9bd5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ed7d31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a5a5a5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="ffc000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472c4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70ad47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563c1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954f72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8678,197 +9073,197 @@
   <sheetData>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D4" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D26" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D29" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C37" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C40" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C43" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C49" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C52" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D53" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C55" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D56" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C58" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -8895,236 +9290,236 @@
   <sheetData>
     <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D28" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C46" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E48" s="24"/>
       <c r="F48" s="24"/>
       <c r="G48" s="24" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H48" s="24"/>
       <c r="I48" s="24"/>
       <c r="J48" s="24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K48" s="24"/>
       <c r="L48" s="24"/>
       <c r="M48" s="24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N48" s="24"/>
       <c r="O48" s="24"/>
       <c r="P48" s="24" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q48" s="24"/>
       <c r="R48" s="24"/>
       <c r="S48" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="T48" s="24"/>
       <c r="U48" s="24"/>
     </row>
     <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C50" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D55" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E61" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E63" s="25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F63" s="25"/>
       <c r="G63" s="25"/>
       <c r="H63" s="25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I63" s="25"/>
       <c r="J63" s="25"/>
       <c r="K63" s="25"/>
       <c r="L63" s="25" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M63" s="25"/>
       <c r="N63" s="25"/>
       <c r="O63" s="25"/>
       <c r="P63" s="25" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q63" s="25"/>
       <c r="R63" s="25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S63" s="25"/>
       <c r="T63" s="25"/>
       <c r="U63" s="25"/>
       <c r="V63" s="25" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="W63" s="25"/>
       <c r="X63" s="25"/>
@@ -9158,18 +9553,18 @@
     </row>
     <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E64" s="26" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F64" s="26"/>
       <c r="G64" s="26"/>
       <c r="H64" s="24" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
       <c r="K64" s="24"/>
       <c r="L64" s="24" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M64" s="24"/>
       <c r="N64" s="24"/>
@@ -9181,7 +9576,7 @@
       <c r="T64" s="24"/>
       <c r="U64" s="24"/>
       <c r="V64" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="W64" s="16"/>
       <c r="X64" s="16"/>
@@ -9218,13 +9613,13 @@
       <c r="F65" s="26"/>
       <c r="G65" s="26"/>
       <c r="H65" s="24" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I65" s="24"/>
       <c r="J65" s="24"/>
       <c r="K65" s="24"/>
       <c r="L65" s="24" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M65" s="24"/>
       <c r="N65" s="24"/>
@@ -9236,7 +9631,7 @@
       <c r="T65" s="24"/>
       <c r="U65" s="24"/>
       <c r="V65" s="27" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="W65" s="28"/>
       <c r="X65" s="28"/>
@@ -9273,7 +9668,7 @@
       <c r="F66" s="26"/>
       <c r="G66" s="26"/>
       <c r="H66" s="24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I66" s="24"/>
       <c r="J66" s="24"/>
@@ -9289,7 +9684,7 @@
       <c r="T66" s="24"/>
       <c r="U66" s="24"/>
       <c r="V66" s="30" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AY66" s="31"/>
     </row>
@@ -9298,13 +9693,13 @@
       <c r="F67" s="26"/>
       <c r="G67" s="26"/>
       <c r="H67" s="24" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I67" s="24"/>
       <c r="J67" s="24"/>
       <c r="K67" s="24"/>
       <c r="L67" s="24" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M67" s="24"/>
       <c r="N67" s="24"/>
@@ -9316,7 +9711,7 @@
       <c r="T67" s="24"/>
       <c r="U67" s="24"/>
       <c r="V67" s="32" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="W67" s="33"/>
       <c r="X67" s="33"/>
@@ -9353,13 +9748,13 @@
       <c r="F68" s="26"/>
       <c r="G68" s="26"/>
       <c r="H68" s="24" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I68" s="24"/>
       <c r="J68" s="24"/>
       <c r="K68" s="24"/>
       <c r="L68" s="24" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M68" s="24"/>
       <c r="N68" s="24"/>
@@ -9371,7 +9766,7 @@
       <c r="T68" s="24"/>
       <c r="U68" s="24"/>
       <c r="V68" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="W68" s="16"/>
       <c r="X68" s="16"/>
@@ -9405,18 +9800,18 @@
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E69" s="35" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F69" s="35"/>
       <c r="G69" s="35"/>
       <c r="H69" s="24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I69" s="24"/>
       <c r="J69" s="24"/>
       <c r="K69" s="24"/>
       <c r="L69" s="24" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M69" s="24"/>
       <c r="N69" s="24"/>
@@ -9424,13 +9819,13 @@
       <c r="P69" s="24"/>
       <c r="Q69" s="24"/>
       <c r="R69" s="24" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="S69" s="24"/>
       <c r="T69" s="24"/>
       <c r="U69" s="24"/>
       <c r="V69" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="W69" s="16"/>
       <c r="X69" s="16"/>
@@ -9467,13 +9862,13 @@
       <c r="F70" s="35"/>
       <c r="G70" s="35"/>
       <c r="H70" s="24" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I70" s="24"/>
       <c r="J70" s="24"/>
       <c r="K70" s="24"/>
       <c r="L70" s="24" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M70" s="24"/>
       <c r="N70" s="24"/>
@@ -9485,7 +9880,7 @@
       <c r="T70" s="24"/>
       <c r="U70" s="24"/>
       <c r="V70" s="15" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="W70" s="16"/>
       <c r="X70" s="16"/>
@@ -9522,29 +9917,29 @@
       <c r="F71" s="35"/>
       <c r="G71" s="35"/>
       <c r="H71" s="24" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I71" s="24"/>
       <c r="J71" s="24"/>
       <c r="K71" s="24"/>
       <c r="L71" s="24" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M71" s="24"/>
       <c r="N71" s="24"/>
       <c r="O71" s="24"/>
       <c r="P71" s="24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q71" s="24"/>
       <c r="R71" s="24" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="S71" s="24"/>
       <c r="T71" s="24"/>
       <c r="U71" s="24"/>
       <c r="V71" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="W71" s="16"/>
       <c r="X71" s="16"/>
@@ -9581,13 +9976,13 @@
       <c r="F72" s="35"/>
       <c r="G72" s="35"/>
       <c r="H72" s="24" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I72" s="24"/>
       <c r="J72" s="24"/>
       <c r="K72" s="24"/>
       <c r="L72" s="24" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M72" s="24"/>
       <c r="N72" s="24"/>
@@ -9599,7 +9994,7 @@
       <c r="T72" s="24"/>
       <c r="U72" s="24"/>
       <c r="V72" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="W72" s="16"/>
       <c r="X72" s="16"/>
@@ -9636,13 +10031,13 @@
       <c r="F73" s="35"/>
       <c r="G73" s="35"/>
       <c r="H73" s="24" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I73" s="24"/>
       <c r="J73" s="24"/>
       <c r="K73" s="24"/>
       <c r="L73" s="24" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M73" s="24"/>
       <c r="N73" s="24"/>
@@ -9650,13 +10045,13 @@
       <c r="P73" s="24"/>
       <c r="Q73" s="24"/>
       <c r="R73" s="24" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="S73" s="24"/>
       <c r="T73" s="24"/>
       <c r="U73" s="24"/>
       <c r="V73" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="W73" s="16"/>
       <c r="X73" s="16"/>
@@ -9693,13 +10088,13 @@
       <c r="F74" s="35"/>
       <c r="G74" s="35"/>
       <c r="H74" s="24" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I74" s="24"/>
       <c r="J74" s="24"/>
       <c r="K74" s="24"/>
       <c r="L74" s="24" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M74" s="24"/>
       <c r="N74" s="24"/>
@@ -9711,7 +10106,7 @@
       <c r="T74" s="24"/>
       <c r="U74" s="24"/>
       <c r="V74" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="W74" s="16"/>
       <c r="X74" s="16"/>
@@ -9748,13 +10143,13 @@
       <c r="F75" s="35"/>
       <c r="G75" s="35"/>
       <c r="H75" s="24" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I75" s="24"/>
       <c r="J75" s="24"/>
       <c r="K75" s="24"/>
       <c r="L75" s="24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M75" s="24"/>
       <c r="N75" s="24"/>
@@ -9766,7 +10161,7 @@
       <c r="T75" s="24"/>
       <c r="U75" s="24"/>
       <c r="V75" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="W75" s="16"/>
       <c r="X75" s="16"/>
@@ -9803,13 +10198,13 @@
       <c r="F76" s="35"/>
       <c r="G76" s="35"/>
       <c r="H76" s="24" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I76" s="24"/>
       <c r="J76" s="24"/>
       <c r="K76" s="24"/>
       <c r="L76" s="24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M76" s="24"/>
       <c r="N76" s="24"/>
@@ -9821,7 +10216,7 @@
       <c r="T76" s="24"/>
       <c r="U76" s="24"/>
       <c r="V76" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W76" s="16"/>
       <c r="X76" s="16"/>
@@ -9858,13 +10253,13 @@
       <c r="F77" s="35"/>
       <c r="G77" s="35"/>
       <c r="H77" s="24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I77" s="24"/>
       <c r="J77" s="24"/>
       <c r="K77" s="24"/>
       <c r="L77" s="24" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M77" s="24"/>
       <c r="N77" s="24"/>
@@ -9876,7 +10271,7 @@
       <c r="T77" s="24"/>
       <c r="U77" s="24"/>
       <c r="V77" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="W77" s="16"/>
       <c r="X77" s="16"/>
@@ -9913,13 +10308,13 @@
       <c r="F78" s="35"/>
       <c r="G78" s="35"/>
       <c r="H78" s="24" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I78" s="24"/>
       <c r="J78" s="24"/>
       <c r="K78" s="24"/>
       <c r="L78" s="24" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M78" s="24"/>
       <c r="N78" s="24"/>
@@ -9931,7 +10326,7 @@
       <c r="T78" s="24"/>
       <c r="U78" s="24"/>
       <c r="V78" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="W78" s="16"/>
       <c r="X78" s="16"/>
@@ -9965,18 +10360,18 @@
     </row>
     <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E79" s="26" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F79" s="26"/>
       <c r="G79" s="26"/>
       <c r="H79" s="24" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I79" s="24"/>
       <c r="J79" s="24"/>
       <c r="K79" s="24"/>
       <c r="L79" s="24" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M79" s="24"/>
       <c r="N79" s="24"/>
@@ -10027,7 +10422,7 @@
       <c r="J80" s="24"/>
       <c r="K80" s="24"/>
       <c r="L80" s="24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M80" s="24"/>
       <c r="N80" s="24"/>
@@ -10078,7 +10473,7 @@
       <c r="J81" s="24"/>
       <c r="K81" s="24"/>
       <c r="L81" s="24" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M81" s="24"/>
       <c r="N81" s="24"/>
@@ -10122,72 +10517,72 @@
     </row>
     <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D83" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E84" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E85" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E86" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E88" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E89" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E90" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E92" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D94" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E95" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D97" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E98" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E99" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E100" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -10557,7 +10952,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="6" t="s">
         <v>59</v>
       </c>
@@ -10567,17 +10962,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="6" t="s">
         <v>63</v>
       </c>
@@ -10817,7 +11212,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="6" t="s">
         <v>98</v>
       </c>
@@ -10882,28 +11277,28 @@
         <v>110</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C174" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C175" s="10"/>
     </row>
-    <row r="176" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C176" s="10" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C177" s="10" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C178" s="10"/>
     </row>
-    <row r="179" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C179" s="1"/>
       <c r="E179" s="3" t="s">
         <v>114</v>
@@ -10914,30 +11309,30 @@
         <v>115</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C209" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C210" s="10"/>
     </row>
-    <row r="211" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C211" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C212" s="10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C213" s="10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C214" s="1"/>
     </row>
     <row r="241" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10945,20 +11340,20 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C242" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C243" s="10"/>
     </row>
-    <row r="244" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C244" s="11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C245" s="11" t="s">
         <v>123</v>
       </c>
@@ -10989,7 +11384,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C287" s="13" t="s">
         <v>127</v>
       </c>
@@ -11098,7 +11493,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="6" t="s">
         <v>141</v>
       </c>
@@ -11270,7 +11665,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D59" s="6" t="s">
         <v>161</v>
       </c>
@@ -11295,7 +11690,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D89" s="6" t="s">
         <v>165</v>
       </c>
@@ -11361,7 +11756,7 @@
       <c r="AA161" s="16"/>
       <c r="AB161" s="17"/>
     </row>
-    <row r="162" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D162" s="18" t="s">
         <v>172</v>
       </c>
@@ -11490,7 +11885,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="6" t="s">
         <v>187</v>
       </c>
@@ -11611,81 +12006,81 @@
         <v>205</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="10" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="10"/>
     </row>
-    <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="10"/>
       <c r="E9" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="10"/>
     </row>
-    <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="10"/>
       <c r="E11" s="6" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="10"/>
       <c r="E12" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="10"/>
       <c r="E13" s="3" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="10"/>
       <c r="E14" s="6" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="10"/>
     </row>
-    <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C16" s="10"/>
     </row>
-    <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="10"/>
     </row>
-    <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="10" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="10"/>
     </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="10"/>
       <c r="F21" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="10"/>
       <c r="F22" s="3" t="s">
         <v>215</v>
@@ -11694,16 +12089,16 @@
         <v>216</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="10"/>
     </row>
-    <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="10"/>
       <c r="F24" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="10"/>
       <c r="F25" s="3" t="s">
         <v>215</v>
@@ -11712,7 +12107,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11735,7 +12130,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="10"/>
       <c r="F31" s="7" t="s">
         <v>222</v>
@@ -11744,13 +12139,13 @@
         <v>223</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="10"/>
       <c r="F32" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11785,7 +12180,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E105"/>
+  <dimension ref="B2:E108"/>
   <sheetFormatPr defaultColWidth="2.78125" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="3" width="2.78"/>
@@ -11821,13 +12216,13 @@
         <v>231</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
         <v>232</v>
       </c>
       <c r="D28" s="10"/>
     </row>
-    <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="3" t="s">
         <v>233</v>
       </c>
@@ -11838,13 +12233,13 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="3" t="s">
         <v>235</v>
       </c>
       <c r="D31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="3" t="s">
         <v>236</v>
       </c>
@@ -11875,7 +12270,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="11.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E104" s="3" t="s">
         <v>242</v>
       </c>
@@ -11883,6 +12278,16 @@
     <row r="105" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E105" s="3" t="s">
         <v>243</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E107" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E108" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
